--- a/Gen 2 Design/Firmware/calibration.xlsx
+++ b/Gen 2 Design/Firmware/calibration.xlsx
@@ -274,6 +274,7 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -453,8 +454,12 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -526,11 +531,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="59181749"/>
-        <c:axId val="59032682"/>
+        <c:axId val="94047739"/>
+        <c:axId val="36826997"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="59181749"/>
+        <c:axId val="94047739"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -553,18 +558,22 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59032682"/>
+        <c:crossAx val="36826997"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="59032682"/>
+        <c:axId val="36826997"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -596,13 +605,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59181749"/>
+        <c:crossAx val="94047739"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -630,8 +643,12 @@
         <a:p>
           <a:pPr>
             <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
               <a:uFillTx/>
               <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -691,8 +708,12 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -764,11 +785,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="34048959"/>
-        <c:axId val="58064052"/>
+        <c:axId val="28345221"/>
+        <c:axId val="16027791"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="34048959"/>
+        <c:axId val="28345221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -791,18 +812,22 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58064052"/>
+        <c:crossAx val="16027791"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="58064052"/>
+        <c:axId val="16027791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -834,13 +859,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34048959"/>
+        <c:crossAx val="28345221"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -868,8 +897,12 @@
         <a:p>
           <a:pPr>
             <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
               <a:uFillTx/>
               <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -900,9 +933,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>130680</xdr:colOff>
+      <xdr:colOff>129960</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>114480</xdr:rowOff>
+      <xdr:rowOff>113760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -911,7 +944,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10406520" y="544680"/>
-        <a:ext cx="6297840" cy="3471120"/>
+        <a:ext cx="6297120" cy="3470400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -935,9 +968,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>404280</xdr:colOff>
+      <xdr:colOff>403560</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>52920</xdr:rowOff>
+      <xdr:rowOff>52200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -946,7 +979,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11119680" y="890640"/>
-        <a:ext cx="5858280" cy="3228840"/>
+        <a:ext cx="5857560" cy="3228120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1070,7 +1103,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K271"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="1" width="11.76"/>
@@ -1094,822 +1127,822 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="n">
-        <v>63157</v>
+        <v>-87430</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-245371</v>
+        <v>-396766</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="n">
-        <v>63138</v>
+        <v>-87476</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-245394</v>
+        <v>-396521</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="n">
-        <v>63152</v>
+        <v>-87308</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-245448</v>
+        <v>-396554</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="n">
         <f aca="false">$B$102</f>
-        <v>63255.8080808081</v>
+        <v>-87437.9595959596</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K5" s="1" t="n">
         <f aca="false">(G5-G6)/(F5-F6)</f>
-        <v>3087.62808080808</v>
+        <v>3093.1604040404</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="n">
-        <v>63188</v>
+        <v>-87399</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-245424</v>
+        <v>-396804</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>-100</v>
       </c>
       <c r="G6" s="1" t="n">
         <f aca="false">$C$97</f>
-        <v>-245507</v>
+        <v>-396754</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K6" s="1" t="n">
         <f aca="false">G5/K5</f>
-        <v>20.4868612492516</v>
+        <v>-28.2681620654864</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="n">
-        <v>63269</v>
+        <v>-87371</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-245334</v>
+        <v>-396942</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="n">
-        <v>63261</v>
+        <v>-87414</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-245353</v>
+        <v>-396601</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="n">
-        <v>63232</v>
+        <v>-87342</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-245368</v>
+        <v>-396880</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="n">
-        <v>63216</v>
+        <v>-87260</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-245406</v>
+        <v>-396742</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="n">
-        <v>63180</v>
+        <v>-87511</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-245453</v>
+        <v>-396405</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="n">
-        <v>63145</v>
+        <v>-87424</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-245414</v>
+        <v>-396663</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="n">
-        <v>63166</v>
+        <v>-87514</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-245379</v>
+        <v>-396592</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="n">
-        <v>63179</v>
+        <v>-87577</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-245420</v>
+        <v>-396845</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="n">
-        <v>63224</v>
+        <v>-87510</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-245432</v>
+        <v>-396735</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="n">
-        <v>63177</v>
+        <v>-87493</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-245409</v>
+        <v>-396950</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="n">
-        <v>63149</v>
+        <v>-87529</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-245427</v>
+        <v>-396656</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="n">
-        <v>63179</v>
+        <v>-87488</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-245434</v>
+        <v>-396976</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="n">
-        <v>63183</v>
+        <v>-87371</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-245414</v>
+        <v>-396705</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="n">
-        <v>63171</v>
+        <v>-87380</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-245391</v>
+        <v>-396938</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="n">
-        <v>63150</v>
+        <v>-87426</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-245384</v>
+        <v>-396558</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="n">
-        <v>63173</v>
+        <v>-87583</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-245366</v>
+        <v>-396768</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="n">
-        <v>63144</v>
+        <v>-87500</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-245419</v>
+        <v>-396662</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="n">
-        <v>63077</v>
+        <v>-87507</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-245364</v>
+        <v>-396922</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="n">
-        <v>63103</v>
+        <v>-87648</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-245329</v>
+        <v>-396486</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="n">
-        <v>63182</v>
+        <v>-87394</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-245356</v>
+        <v>-396636</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="n">
-        <v>63225</v>
+        <v>-87487</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-245344</v>
+        <v>-396853</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="n">
-        <v>63225</v>
+        <v>-87606</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>-245366</v>
+        <v>-396675</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="n">
-        <v>63206</v>
+        <v>-87320</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>-245340</v>
+        <v>-396620</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="n">
-        <v>63247</v>
+        <v>-87334</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>-245350</v>
+        <v>-396693</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="n">
-        <v>63228</v>
+        <v>-87364</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>-245338</v>
+        <v>-396686</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="n">
-        <v>63201</v>
+        <v>-87241</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>-245319</v>
+        <v>-396622</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="n">
-        <v>63200</v>
+        <v>-87359</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>-245305</v>
+        <v>-396623</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="n">
-        <v>63172</v>
+        <v>-87460</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>-245399</v>
+        <v>-396753</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="n">
-        <v>63261</v>
+        <v>-87430</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>-245463</v>
+        <v>-396576</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="n">
-        <v>63282</v>
+        <v>-87482</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-245411</v>
+        <v>-396769</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="n">
-        <v>63298</v>
+        <v>-87407</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>-245399</v>
+        <v>-396545</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="n">
-        <v>63315</v>
+        <v>-87400</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>-245381</v>
+        <v>-396636</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="2" t="n">
-        <v>63316</v>
+        <v>-87432</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>-245393</v>
+        <v>-396678</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="n">
-        <v>63249</v>
+        <v>-87453</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-245319</v>
+        <v>-396719</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="2" t="n">
-        <v>63212</v>
+        <v>-87412</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>-245284</v>
+        <v>-396781</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="n">
-        <v>63254</v>
+        <v>-87419</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>-245335</v>
+        <v>-396738</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="n">
-        <v>63278</v>
+        <v>-87419</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>-245359</v>
+        <v>-396838</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="2" t="n">
-        <v>63236</v>
+        <v>-87478</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>-245374</v>
+        <v>-396680</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="2" t="n">
-        <v>63232</v>
+        <v>-87436</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>-245302</v>
+        <v>-396627</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="2" t="n">
-        <v>63251</v>
+        <v>-87417</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>-245285</v>
+        <v>-396741</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="2" t="n">
-        <v>63260</v>
+        <v>-87332</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>-245312</v>
+        <v>-396640</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="2" t="n">
-        <v>63245</v>
+        <v>-87343</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>-245360</v>
+        <v>-396759</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="2" t="n">
-        <v>63210</v>
+        <v>-87223</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>-245376</v>
+        <v>-396772</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="2" t="n">
-        <v>63177</v>
+        <v>-87490</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>-245364</v>
+        <v>-396468</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="2" t="n">
-        <v>63212</v>
+        <v>-87559</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>-245363</v>
+        <v>-396524</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="2" t="n">
-        <v>63222</v>
+        <v>-87424</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>-245375</v>
+        <v>-396749</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="2" t="n">
-        <v>63216</v>
+        <v>-87580</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>-245316</v>
+        <v>-396609</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="2" t="n">
-        <v>63309</v>
+        <v>-87547</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>-245326</v>
+        <v>-396671</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="1" t="n">
-        <v>63300</v>
+        <v>-87591</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>-245382</v>
+        <v>-396652</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="1" t="n">
-        <v>63263</v>
+        <v>-87477</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>-245307</v>
+        <v>-396523</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="n">
-        <v>63307</v>
+        <v>-87339</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>-245276</v>
+        <v>-396767</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="n">
-        <v>63322</v>
+        <v>-87415</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>-245270</v>
+        <v>-396811</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="1" t="n">
-        <v>63323</v>
+        <v>-87497</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>-245296</v>
+        <v>-396690</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="1" t="n">
-        <v>63301</v>
+        <v>-87450</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>-245241</v>
+        <v>-396309</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="1" t="n">
-        <v>63293</v>
+        <v>-87556</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>-245240</v>
+        <v>-396852</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="1" t="n">
-        <v>63268</v>
+        <v>-87394</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>-245260</v>
+        <v>-396591</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="n">
-        <v>63303</v>
+        <v>-87403</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>-245323</v>
+        <v>-396031</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="1" t="n">
-        <v>63342</v>
+        <v>-87322</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>-245349</v>
+        <v>-396616</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="1" t="n">
-        <v>63301</v>
+        <v>-87322</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>-245391</v>
+        <v>-396865</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="1" t="n">
-        <v>63314</v>
+        <v>-87353</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>-245378</v>
+        <v>-396614</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="n">
-        <v>63299</v>
+        <v>-87475</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>-245394</v>
+        <v>-396122</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="1" t="n">
-        <v>63287</v>
+        <v>-87494</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>-245391</v>
+        <v>-397602</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="1" t="n">
-        <v>63287</v>
+        <v>-87584</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>-245386</v>
+        <v>-396950</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="1" t="n">
-        <v>63351</v>
+        <v>-87360</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>-245410</v>
+        <v>-396415</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="n">
-        <v>63345</v>
+        <v>-87532</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>-245389</v>
+        <v>-396691</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="1" t="n">
-        <v>63343</v>
+        <v>-87320</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>-245418</v>
+        <v>-396430</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="n">
-        <v>63386</v>
+        <v>-87440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>-245440</v>
+        <v>-396750</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="1" t="n">
-        <v>63410</v>
+        <v>-87632</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>-245437</v>
+        <v>-396919</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="1" t="n">
-        <v>63392</v>
+        <v>-87402</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>-245453</v>
+        <v>-396587</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="n">
-        <v>63377</v>
+        <v>-87472</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>-245469</v>
+        <v>-396485</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="1" t="n">
-        <v>63366</v>
+        <v>-87465</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>-245424</v>
+        <v>-396653</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="1" t="n">
-        <v>63338</v>
+        <v>-87288</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>-245399</v>
+        <v>-396512</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="1" t="n">
-        <v>63337</v>
+        <v>-87500</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>-245412</v>
+        <v>-396744</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="1" t="n">
-        <v>63298</v>
+        <v>-87400</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>-245409</v>
+        <v>-396740</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="1" t="n">
-        <v>63298</v>
+        <v>-87428</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>-245431</v>
+        <v>-396440</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="1" t="n">
-        <v>63299</v>
+        <v>-87314</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>-245405</v>
+        <v>-396495</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="1" t="n">
-        <v>63309</v>
+        <v>-87459</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>-245449</v>
+        <v>-396775</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="1" t="n">
-        <v>63272</v>
+        <v>-87459</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>-245460</v>
+        <v>-396663</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="1" t="n">
-        <v>63205</v>
+        <v>-87494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>-245460</v>
+        <v>-396631</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="1" t="n">
-        <v>63270</v>
+        <v>-87311</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>-245496</v>
+        <v>-396653</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="1" t="n">
-        <v>63298</v>
+        <v>-87411</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>-245544</v>
+        <v>-396733</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="1" t="n">
-        <v>63244</v>
+        <v>-87437</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>-245549</v>
+        <v>-396485</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="1" t="n">
-        <v>63214</v>
+        <v>-87349</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>-245487</v>
+        <v>-396422</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="1" t="n">
-        <v>63217</v>
+        <v>-87590</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>-245426</v>
+        <v>-396389</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="1" t="n">
-        <v>63231</v>
+        <v>-87518</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>-245436</v>
+        <v>-396753</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="1" t="n">
-        <v>63335</v>
+        <v>-87591</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>-245492</v>
+        <v>-396386</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="1" t="n">
-        <v>63331</v>
+        <v>-87413</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>-245458</v>
+        <v>-396697</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="1" t="n">
-        <v>63290</v>
+        <v>-87342</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>-245442</v>
+        <v>-396276</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="1" t="n">
-        <v>63308</v>
+        <v>-87369</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>-245446</v>
+        <v>-396687</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="1" t="n">
-        <v>63324</v>
+        <v>-87567</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>-245465</v>
+        <v>-396563</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="1" t="n">
-        <v>63300</v>
+        <v>-87481</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>-245507</v>
+        <v>-396754</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="1" t="n">
-        <v>63324</v>
+        <v>-87325</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>-245478</v>
+        <v>-396705</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="1" t="n">
-        <v>63344</v>
+        <v>-87546</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>-245454</v>
+        <v>-396611</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="1" t="n">
-        <v>63267</v>
+        <v>-87396</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>-245437</v>
+        <v>-396785</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="1" t="n">
-        <v>63258</v>
+        <v>-87366</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>-245453</v>
+        <v>-397325</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1918,150 +1951,964 @@
       </c>
       <c r="B102" s="1" t="n">
         <f aca="false">AVERAGE(B3:B101)</f>
-        <v>63255.8080808081</v>
+        <v>-87437.9595959596</v>
       </c>
       <c r="C102" s="1" t="n">
         <f aca="false">AVERAGE(C3:C101)</f>
-        <v>-245390.565656566</v>
+        <v>-396671.727272727</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="1" t="n">
-        <v>63288</v>
+        <v>-87433</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>-245470</v>
+        <v>-396362</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="1" t="n">
-        <v>63328</v>
+        <v>-87357</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>-245466</v>
+        <v>-396662</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="1" t="n">
-        <v>63343</v>
+        <v>-87373</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>-245490</v>
+        <v>-396443</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="1" t="n">
+        <v>-87298</v>
+      </c>
       <c r="C106" s="1" t="n">
-        <v>-245431</v>
+        <v>-396621</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="1" t="n">
+        <v>-87516</v>
+      </c>
       <c r="C107" s="1" t="n">
-        <v>-245408</v>
+        <v>-396858</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="1" t="n">
+        <v>-87483</v>
+      </c>
       <c r="C108" s="1" t="n">
-        <v>-245407</v>
+        <v>-396565</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="1" t="n">
+        <v>-87230</v>
+      </c>
       <c r="C109" s="1" t="n">
-        <v>-245362</v>
+        <v>-396203</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="1" t="n">
+        <v>-87471</v>
+      </c>
       <c r="C110" s="1" t="n">
-        <v>-245363</v>
+        <v>-396900</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="1" t="n">
+        <v>-87621</v>
+      </c>
       <c r="C111" s="1" t="n">
-        <v>-245342</v>
+        <v>-396651</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="1" t="n">
+        <v>-87381</v>
+      </c>
       <c r="C112" s="1" t="n">
-        <v>-245377</v>
+        <v>-396661</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="1" t="n">
+        <v>-87413</v>
+      </c>
       <c r="C113" s="1" t="n">
-        <v>-245407</v>
+        <v>-396571</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="1" t="n">
+        <v>-87382</v>
+      </c>
       <c r="C114" s="1" t="n">
-        <v>-245441</v>
+        <v>-396439</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="1" t="n">
+        <v>-87426</v>
+      </c>
       <c r="C115" s="1" t="n">
-        <v>-245460</v>
+        <v>-396520</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="1" t="n">
+        <v>-87523</v>
+      </c>
       <c r="C116" s="1" t="n">
-        <v>-245445</v>
+        <v>-396426</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="1" t="n">
+        <v>-87400</v>
+      </c>
       <c r="C117" s="1" t="n">
-        <v>-245372</v>
+        <v>-396477</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="1" t="n">
+        <v>-87302</v>
+      </c>
       <c r="C118" s="1" t="n">
-        <v>-245322</v>
+        <v>-396536</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="1" t="n">
+        <v>-87300</v>
+      </c>
       <c r="C119" s="1" t="n">
-        <v>-245351</v>
+        <v>-396461</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="1" t="n">
+        <v>-87354</v>
+      </c>
       <c r="C120" s="1" t="n">
-        <v>-245412</v>
+        <v>-396467</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="1" t="n">
+        <v>-87468</v>
+      </c>
       <c r="C121" s="1" t="n">
-        <v>-245420</v>
+        <v>-396678</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="1" t="n">
+        <v>-87504</v>
+      </c>
       <c r="C122" s="1" t="n">
-        <v>-245416</v>
+        <v>-396632</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="1" t="n">
+        <v>-87498</v>
+      </c>
       <c r="C123" s="1" t="n">
-        <v>-245417</v>
+        <v>-396550</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="1" t="n">
+        <v>-87394</v>
+      </c>
       <c r="C124" s="1" t="n">
-        <v>-245417</v>
+        <v>-396502</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="1" t="n">
+        <v>-87630</v>
+      </c>
       <c r="C125" s="1" t="n">
-        <v>-245439</v>
+        <v>-225510</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="1" t="n">
+        <v>-87386</v>
+      </c>
       <c r="C126" s="1" t="n">
-        <v>-245407</v>
+        <v>-225546</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="1" t="n">
+        <v>-87476</v>
+      </c>
       <c r="C127" s="1" t="n">
-        <v>-245413</v>
+        <v>-225692</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="1" t="n">
+        <v>-87217</v>
+      </c>
       <c r="C128" s="1" t="n">
-        <v>-245399</v>
+        <v>-225461</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="1" t="n">
+        <v>-87315</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>-234965</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="1" t="n">
+        <v>-87403</v>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>-234898</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="1" t="n">
+        <v>-87245</v>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>-234906</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="1" t="n">
+        <v>-87469</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>-234934</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="1" t="n">
+        <v>-87529</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>-234986</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="1" t="n">
+        <v>-87624</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>-234951</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="1" t="n">
+        <v>-87514</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>-234909</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="1" t="n">
+        <v>-87405</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>-234925</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="1" t="n">
+        <v>-87498</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>-234953</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="1" t="n">
+        <v>-87455</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>-234965</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="1" t="n">
+        <v>-87545</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="1" t="n">
+        <v>-87533</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="1" t="n">
+        <v>-87465</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="1" t="n">
+        <v>-87394</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B143" s="1" t="n">
+        <v>-87569</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B144" s="1" t="n">
+        <v>-87469</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B145" s="1" t="n">
+        <v>-87386</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="1" t="n">
+        <v>-87422</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="1" t="n">
+        <v>-87430</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="1" t="n">
+        <v>-87541</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="1" t="n">
+        <v>-87385</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="1" t="n">
+        <v>-87398</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B151" s="1" t="n">
+        <v>-87495</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="1" t="n">
+        <v>-87314</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="1" t="n">
+        <v>-87357</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="1" t="n">
+        <v>-87271</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="1" t="n">
+        <v>-87414</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="1" t="n">
+        <v>-87323</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="1" t="n">
+        <v>-87390</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="1" t="n">
+        <v>-87304</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="1" t="n">
+        <v>-87436</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="1" t="n">
+        <v>-87258</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B161" s="1" t="n">
+        <v>-87350</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B162" s="1" t="n">
+        <v>-87675</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="1" t="n">
+        <v>-87318</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B164" s="1" t="n">
+        <v>-87472</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B165" s="1" t="n">
+        <v>-87441</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B166" s="1" t="n">
+        <v>-87480</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="1" t="n">
+        <v>-87542</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="1" t="n">
+        <v>-87335</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="1" t="n">
+        <v>-87427</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="1" t="n">
+        <v>-87424</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B171" s="1" t="n">
+        <v>-87393</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="1" t="n">
+        <v>-87492</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B173" s="1" t="n">
+        <v>-87478</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B174" s="1" t="n">
+        <v>-87480</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="1" t="n">
+        <v>-87470</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="1" t="n">
+        <v>-87340</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="1" t="n">
+        <v>-87464</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="1" t="n">
+        <v>-87363</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="1" t="n">
+        <v>-87414</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B180" s="1" t="n">
+        <v>-87465</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B181" s="1" t="n">
+        <v>-87395</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B182" s="1" t="n">
+        <v>-87440</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B183" s="1" t="n">
+        <v>88236</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B184" s="1" t="n">
+        <v>88215</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B185" s="1" t="n">
+        <v>88259</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B186" s="1" t="n">
+        <v>88159</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B187" s="1" t="n">
+        <v>88387</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B188" s="1" t="n">
+        <v>88391</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B189" s="1" t="n">
+        <v>88306</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B190" s="1" t="n">
+        <v>88148</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B191" s="1" t="n">
+        <v>88202</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="1" t="n">
+        <v>88281</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B193" s="1" t="n">
+        <v>88222</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B194" s="1" t="n">
+        <v>88344</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B195" s="1" t="n">
+        <v>88485</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B196" s="1" t="n">
+        <v>88456</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="1" t="n">
+        <v>88286</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B198" s="1" t="n">
+        <v>88400</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B199" s="1" t="n">
+        <v>88594</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="1" t="n">
+        <v>88408</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B201" s="1" t="n">
+        <v>88610</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B202" s="1" t="n">
+        <v>88559</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B203" s="1" t="n">
+        <v>88798</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B204" s="1" t="n">
+        <v>88602</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="1" t="n">
+        <v>88704</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="1" t="n">
+        <v>88695</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="1" t="n">
+        <v>88849</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B208" s="1" t="n">
+        <v>88761</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B209" s="1" t="n">
+        <v>88979</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="1" t="n">
+        <v>88846</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="1" t="n">
+        <v>88885</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="1" t="n">
+        <v>88882</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="1" t="n">
+        <v>88810</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="1" t="n">
+        <v>88771</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="1" t="n">
+        <v>88604</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="1" t="n">
+        <v>88719</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="1" t="n">
+        <v>88501</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="1" t="n">
+        <v>88825</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="1" t="n">
+        <v>88740</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B220" s="1" t="n">
+        <v>88716</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B221" s="1" t="n">
+        <v>88753</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B222" s="1" t="n">
+        <v>88735</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B223" s="1" t="n">
+        <v>88642</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B224" s="1" t="n">
+        <v>88779</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B225" s="1" t="n">
+        <v>88791</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B226" s="1" t="n">
+        <v>88603</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B227" s="1" t="n">
+        <v>88654</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B228" s="1" t="n">
+        <v>88586</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B229" s="1" t="n">
+        <v>88563</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B230" s="1" t="n">
+        <v>88660</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B231" s="1" t="n">
+        <v>88009</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B232" s="1" t="n">
+        <v>88013</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B233" s="1" t="n">
+        <v>87842</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B234" s="1" t="n">
+        <v>87928</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B235" s="1" t="n">
+        <v>87966</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B236" s="1" t="n">
+        <v>88044</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B237" s="1" t="n">
+        <v>88109</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B238" s="1" t="n">
+        <v>87968</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B239" s="1" t="n">
+        <v>87890</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B240" s="1" t="n">
+        <v>88184</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B241" s="1" t="n">
+        <v>88217</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B242" s="1" t="n">
+        <v>88236</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B243" s="1" t="n">
+        <v>88277</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B244" s="1" t="n">
+        <v>88180</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B245" s="1" t="n">
+        <v>88472</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B246" s="1" t="n">
+        <v>88399</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B247" s="1" t="n">
+        <v>88164</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B248" s="1" t="n">
+        <v>88318</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B249" s="1" t="n">
+        <v>88455</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B250" s="1" t="n">
+        <v>80545</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B251" s="1" t="n">
+        <v>80545</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B252" s="1" t="n">
+        <v>80541</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B253" s="1" t="n">
+        <v>80515</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B254" s="1" t="n">
+        <v>80507</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B255" s="1" t="n">
+        <v>80517</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B256" s="1" t="n">
+        <v>80494</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B257" s="1" t="n">
+        <v>80502</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B258" s="1" t="n">
+        <v>80509</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B259" s="1" t="n">
+        <v>80507</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B260" s="1" t="n">
+        <v>80580</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B261" s="1" t="n">
+        <v>80587</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B262" s="1" t="n">
+        <v>80554</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B263" s="1" t="n">
+        <v>80522</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B264" s="1" t="n">
+        <v>80535</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B265" s="1" t="n">
+        <v>80453</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B266" s="1" t="n">
+        <v>80410</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B267" s="1" t="n">
+        <v>80461</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B268" s="1" t="n">
+        <v>80451</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B269" s="1" t="n">
+        <v>80404</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B270" s="1" t="n">
+        <v>80438</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B271" s="1" t="n">
+        <v>80468</v>
       </c>
     </row>
   </sheetData>
